--- a/SourceData/Datas/flag.xlsx
+++ b/SourceData/Datas/flag.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="18400" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="flag" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="flag" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1183,7 +1183,6 @@
           <t>拜访镇长府</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -1196,7 +1195,6 @@
           <t>商店购物</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -1209,7 +1207,6 @@
           <t>商店出售</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -1222,7 +1219,6 @@
           <t>接取公告板</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -1235,7 +1231,6 @@
           <t>拜访木工坊</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -1248,7 +1243,6 @@
           <t>探访社区中心</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -1261,7 +1255,6 @@
           <t>春厅立项签字</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -1274,7 +1267,6 @@
           <t>拜访微光诊所</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -1321,7 +1313,19 @@
           <t>点亮春厅</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sleep_first</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>第一夜入睡</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
